--- a/samples/微电子贯通项目/贯通项目评分量规.xlsx
+++ b/samples/微电子贯通项目/贯通项目评分量规.xlsx
@@ -929,7 +929,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>wqlab test --ref：6/6</t>
+          <t>wqlab test --ref：全部通过</t>
         </is>
       </c>
     </row>
